--- a/jpcore-r4b/develop/StructureDefinition-jp-observation-radiology-impression.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-observation-radiology-impression.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -661,7 +661,7 @@
     <t>このObservationを分類するコード。(imaging)が指定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -2018,7 +2018,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.76171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.0859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4b/develop/StructureDefinition-jp-observation-radiology-impression.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-observation-radiology-impression.xlsx
@@ -285,8 +285,8 @@
     <t>画像診断レポートの結論（インプレッション）に対応するObservationプロファイル</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -317,13 +317,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -336,16 +336,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -356,13 +356,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -375,19 +375,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -407,13 +407,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -433,19 +433,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -463,33 +463,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -505,7 +506,7 @@
     <t>このObservationリソースの一意な識別ID</t>
   </si>
   <si>
-    <t>Allows observations to be distinguished and referenced.</t>
+    <t>観測を区別し、参照することを可能にします。 / Allows observations to be distinguished and referenced.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -537,7 +538,7 @@
     <t>このObservationが生成されることになった画像検査に関するオーダ情報</t>
   </si>
   <si>
-    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+    <t>イベントの許可を追跡し、提案/勧告が行われたかどうかを追跡することができます。 / Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -584,13 +585,13 @@
     <t>このリソースは現在有効でないというマークをするコードを含んでいるため、この要素はモディファイアー（修飾的要素）として位置づけられている。</t>
   </si>
   <si>
-    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+    <t>個々の結果のステータスを追跡する必要があります。レポート全体が最終決定される前に、いくつかの結果が確定します。 / Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>Codes providing the status of an observation.</t>
+    <t>観察のステータスを提供するコード。 / Codes providing the status of an observation.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
@@ -624,10 +625,10 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
+    <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.3.0</t>
@@ -655,7 +656,7 @@
     <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
   </si>
   <si>
-    <t>A code that classifies the general type of observation being made.</t>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
   </si>
   <si>
     <t>このObservationを分類するコード。(imaging)が指定される。</t>
@@ -670,10 +671,10 @@
     <t>Observation.category.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -688,7 +689,7 @@
     <t>Observation.category.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -711,16 +712,16 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -750,16 +751,16 @@
     <t>Observation.category.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
@@ -784,13 +785,13 @@
 </t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
   </si>
   <si>
     <t>Coding.version</t>
@@ -808,13 +809,13 @@
     <t>Observation.category.coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>imaging</t>
@@ -835,13 +836,13 @@
     <t>Observation.category.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -863,16 +864,16 @@
 </t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
   </si>
   <si>
     <t>Coding.userSelected</t>
@@ -890,16 +891,16 @@
     <t>Observation.category.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -924,13 +925,13 @@
     <t>observation(インプレッション)を表すLOINCコード。19005-8, Radiology Imaging study [Impression] (narrative)が指定される。</t>
   </si>
   <si>
-    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+    <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Codes identifying names of simple observations.</t>
+    <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.3.0</t>
@@ -1006,7 +1007,7 @@
     <t>このObservationの対象となる患者。</t>
   </si>
   <si>
-    <t>Observations have no value if you don't know who or what they're about.</t>
+    <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1054,7 +1055,7 @@
     <t>通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、その場合でもEncounterのコンテキストに関連付けられている（例：入院前の臨床検査）。</t>
   </si>
   <si>
-    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
+    <t>一部の観察では、観察と特定のEncounterの間のリンクを知ることが重要かもしれません。 / For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1086,7 +1087,7 @@
     <t>「結論」が生成された日時(DateTime)。</t>
   </si>
   <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+    <t>観察が真実と見なされた時期を知ることは、その関連性にとって重要であり、傾向を決定します。 / Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1136,7 +1137,7 @@
     <t>「結論」を生成した医療者。通常は読影医。</t>
   </si>
   <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+    <t>観察にある程度の自信を与える可能性があり、また、フォローアップの質問をどこに向けるべきかを示します。 / May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1160,7 +1161,7 @@
     <t>「結論」の内容。</t>
   </si>
   <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+    <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1188,13 +1189,13 @@
     <t>ヌル値または例外値は、FHIRオブザベーションで2つの方法で表すことができる。 1つの方法は、それらを値セットに含めて、値の例外を表す方法である。たとえば、血清学的検査の測定値は、「検出された」、「検出されなかった」、「決定的でない」、または「検体が不十分」である可能性がある。別の方法は、実際の観測にvalue要素を使用し、明示的なdataAbsentReason要素を使用して例外的な値を記録することである。たとえば、測定が完了しなかった場合、dataAbsentReasonコード「error」を使用できる。この場合には、観測値は、報告する値がある場合にのみ報告される可能性があることに注意する必要がある。たとえば、差分セルカウント値は&gt; 0の場合にのみ報告される場合がある。これらのオプションのため、nullまたは例外値の一般的な観測値を解釈するにはユースケースの合意が必要である。</t>
   </si>
   <si>
-    <t>For many results it is necessary to handle exceptional values in measurements.</t>
+    <t>多くの結果には、測定で例外的な値を処理する必要があります。 / For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.3.0</t>
@@ -1223,7 +1224,7 @@
     <t>一部の結果、特に数値結果については、結果の意義を完全に理解するためには解釈コードが必要である。</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
+    <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.3.0</t>
@@ -1269,11 +1270,12 @@
     <t>対象となった身体部位</t>
   </si>
   <si>
-    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
+    <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
+ユースケースでは、ボディサイトを個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>SNOMED CT身体部位概念 / SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
@@ -1297,13 +1299,13 @@
     <t>このObservationの実施方法</t>
   </si>
   <si>
-    <t>Only used if not implicit in code for Observation.code.</t>
-  </si>
-  <si>
-    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>Methods for simple observations.</t>
+    <t>CODERATION.CODEのコードに暗黙的ではない場合にのみ使用されます。 / Only used if not implicit in code for Observation.code.</t>
+  </si>
+  <si>
+    <t>場合によっては、メソッドは結果に影響を与える可能性があるため、結果を比較できるか、結果の重要性を決定できるかどうかを判断するために使用されます。 / In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
+  </si>
+  <si>
+    <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-methods|4.3.0</t>
@@ -1381,8 +1383,8 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1404,10 +1406,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1421,10 +1424,10 @@
 </t>
   </si>
   <si>
-    <t>Low Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
+    <t>関連する場合は低レンジ / Low Range, if relevant</t>
+  </si>
+  <si>
+    <t>参照範囲の低境界の値。参照範囲のエンドポイントの低い境界には、値が含まれています（例：参照範囲は&gt; = 5- &lt;= 9）。下限が省略されている場合、それは意味がないと想定されます（例：参照範囲は&lt;= 2.3）。 / The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
   </si>
   <si>
     <t xml:space="preserve">obs-3
@@ -1440,10 +1443,10 @@
     <t>Observation.referenceRange.high</t>
   </si>
   <si>
-    <t>High Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
+    <t>関連する場合、高レンジ / High Range, if relevant</t>
+  </si>
+  <si>
+    <t>参照範囲の強境界の値。参照範囲のエンドポイントの高境界には、値が含まれています（例：参照範囲は&gt; = 5- &lt;= 9）。高バウンドが省略されている場合、それは無意味であると想定されます（例：参照範囲は&gt; = 2.3）。 / The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
   </si>
   <si>
     <t>value:IVL_PQ.high</t>
@@ -1452,19 +1455,19 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>Reference range qualifier</t>
-  </si>
-  <si>
-    <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Code for the meaning of a reference range.</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
+  </si>
+  <si>
+    <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
+  </si>
+  <si>
+    <t>複数の範囲がある場合は、これに浸透する必要があります。この要素が存在しない場合、通常の範囲が想定されます。 / This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
+  </si>
+  <si>
+    <t>適切な解釈のために、これが正常、推奨、治療など、どのような参照範囲を言うことができる必要があります。 / Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
+  </si>
+  <si>
+    <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.3.0</t>
@@ -1485,19 +1488,19 @@
     <t>Observation.referenceRange.appliesTo</t>
   </si>
   <si>
-    <t>Reference range population</t>
-  </si>
-  <si>
-    <t>Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to identify the target population for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Codes identifying the population the reference range applies to.</t>
+    <t>参照範囲の母集団 / Reference range population</t>
+  </si>
+  <si>
+    <t>この参照範囲が適用される対象母集団を示すコード。たとえば、参照範囲は、通常の集団または特定の性別または人種に基づいている場合があります。複数の「Applesto」は、ターゲット集団の「および」として解釈されます。たとえば、アフリカ系アメリカ人の女性の対象集団を代表するために、女性のコードとアフリカ系アメリカ人のコードの両方が使用されます。 / Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
+  </si>
+  <si>
+    <t>複数の範囲がある場合は、これに浸透する必要があります。この要素が存在しない場合、通常の母集団が想定されます。 / This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
+  </si>
+  <si>
+    <t>適切な解釈のためにターゲット母集団を特定できる必要があります。 / Need to be able to identify the target population for proper interpretation.</t>
+  </si>
+  <si>
+    <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.3.0</t>
@@ -1510,13 +1513,13 @@
 </t>
   </si>
   <si>
-    <t>Applicable age range, if relevant</t>
-  </si>
-  <si>
-    <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
-  </si>
-  <si>
-    <t>Some analytes vary greatly over age.</t>
+    <t>適用される年齢範囲、関連する場合 / Applicable age range, if relevant</t>
+  </si>
+  <si>
+    <t>この参照範囲が適用される年齢。意味がそう言っている場合、これは新生児の年齢（期間の週数）です。 / The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
+  </si>
+  <si>
+    <t>一部の分析物は、年齢によって大きく異なります。 / Some analytes vary greatly over age.</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=PRCN].targetObservationCriterion[code="age"].value</t>
@@ -1525,10 +1528,10 @@
     <t>Observation.referenceRange.text</t>
   </si>
   <si>
-    <t>Text based reference range in an observation</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
+    <t>観察中のテキストベースの参照範囲 / Text based reference range in an observation</t>
+  </si>
+  <si>
+    <t>テキストベースの参照範囲の観測では、定量的範囲が観測に適していない場合に使用される場合があります。例は、「ネガティブ」の参照値、または「通常」のリストまたはテーブルです。 / Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
   </si>
   <si>
     <t>value:ST</t>
@@ -1577,7 +1580,7 @@
     <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1599,13 +1602,13 @@
     <t>Observation.component.code</t>
   </si>
   <si>
-    <t>Type of component observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "code".</t>
-  </si>
-  <si>
-    <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+    <t>コンポーネント検査の種類（コード / タイプ） / Type of component observation (code / type)</t>
+  </si>
+  <si>
+    <t>観察されたものについて説明します。これは、「コード」と呼ばれることがあります。 / Describes what was observed. Sometimes this is called the observation "code".</t>
+  </si>
+  <si>
+    <t>*すべて* code-valueおよびcomponent.code-component.valueペアを考慮する必要があります。観察の意味を正しく理解する必要があります。 / *All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1619,13 +1622,13 @@
 CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
-    <t>Actual component result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
-  </si>
-  <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>実際のコンポーネントの結果 / Actual component result</t>
+  </si>
+  <si>
+    <t>情報が単純な値を持っている場合、観察結果の結果として決定された情報。 / The information determined as a result of making the observation, if the information has a simple value.</t>
+  </si>
+  <si>
+    <t>観察には一連のコンポーネント観測がある場合に使用されます。観察には、値（APGARスコアなど）とコンポーネントの観測（APGARスコアが導き出された観測）の両方があります。値が存在する場合、この要素のデータ型は、viscervation.codeによって決定する必要があります。フィールドが通常コーディングされている場合、または観測に関連付けられたタイプの場合、文字列の代わりにテキストのみを持つCodeableconecteが使用されます。コードはコード化された値を定義します。追加のガイダンスについては、以下の[[メモ]セクション]（[観察.html＃注）を参照してください。 / Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -1634,44 +1637,45 @@
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the component result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+    <t>コンポーネントの結果が欠落している理由 / Why the component result is missing</t>
+  </si>
+  <si>
+    <t>Element obervation.component.value [x]の期待値が欠落している理由を提供します。 / Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
   </si>
   <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
-  </si>
-  <si>
-    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+    <t>高、低、正常など。 / High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>観測値のカテゴリー評価。たとえば、高、低、正常。 / A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>歴史的に実験室の結果（「異常なフラグ」と呼ばれる）に使用されていたため、その使用は、コード化された解釈が関連する他のユースケースにまで及びます。多くの場合、1つ以上の単純なコンパクトコードとして報告されているこの要素は、結果の意味/正常性のステータスを示すレポートとフローシートの結果値に隣接することがよくあります。 / Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
+  </si>
+  <si>
+    <t>いくつかの結果、特に数値の結果については、結果の重要性を完全に理解するために解釈が必要です。 / For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
   </si>
   <si>
-    <t>Provides guide for interpretation of component result</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
-  </si>
-  <si>
-    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
-  </si>
-  <si>
-    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
+    <t>コンポーネント結果の解釈のためのガイドを提供します / Provides guide for interpretation of component result</t>
+  </si>
+  <si>
+    <t>通常または推奨範囲と比較して、値を解釈する方法に関するガイダンス。 / Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>ほとんどの観測には、一般的な参照範囲が1つしかありません。システムは、患者に関する知識（患者の年齢、性別、体重、その他の要因に固有）に基づいて、関連する参照範囲のみを供給することを制限することを選択できますが、これは不可能または適切ではない場合があります。複数の参照範囲が提供される場合は、それらの間の違いを参照範囲および/または年齢特性で提供する必要があります。 / Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
+  </si>
+  <si>
+    <t>どの値が「正常」と見なされるかを知ることは、特定の結果の重要性を評価するのに役立ちます。さまざまなコンテキストに複数の参照範囲を提供できる必要があります。 / Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
 </sst>
 </file>
@@ -2017,7 +2021,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="62.0859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
